--- a/parsed-natural-stories.xlsx
+++ b/parsed-natural-stories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\GitHub\naturalstories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AAE0F9-516B-45E7-ADCB-FBA3DB61B726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E913635-F08A-43D4-AE65-7E491A234F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_Boar" sheetId="1" r:id="rId1"/>
@@ -10316,7 +10316,7 @@
   <cols>
     <col min="1" max="1" width="4.08984375" customWidth="1"/>
     <col min="2" max="2" width="109.81640625" customWidth="1"/>
-    <col min="3" max="3" width="0.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" customWidth="1"/>
     <col min="4" max="4" width="6.7265625" customWidth="1"/>
     <col min="27" max="27" width="20.7265625" customWidth="1"/>
     <col min="28" max="28" width="19.81640625" customWidth="1"/>
@@ -10327,7 +10327,7 @@
     <col min="42" max="42" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10455,7 +10455,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -10513,7 +10513,7 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -10577,7 +10577,7 @@
       <c r="AS3" s="1"/>
       <c r="AT3" s="1"/>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -10643,7 +10643,7 @@
       <c r="AS4" s="1"/>
       <c r="AT4" s="1"/>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -10701,7 +10701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -10759,7 +10759,7 @@
       <c r="AS6" s="1"/>
       <c r="AT6" s="1"/>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -10819,7 +10819,7 @@
       <c r="AS7" s="1"/>
       <c r="AT7" s="1"/>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -10877,7 +10877,7 @@
       <c r="AS8" s="1"/>
       <c r="AT8" s="1"/>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -10935,7 +10935,7 @@
       <c r="AS9" s="1"/>
       <c r="AT9" s="1"/>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -10995,7 +10995,7 @@
       <c r="AS10" s="1"/>
       <c r="AT10" s="1"/>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -11055,7 +11055,7 @@
       <c r="AS11" s="1"/>
       <c r="AT11" s="1"/>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -11115,7 +11115,7 @@
       <c r="AS12" s="1"/>
       <c r="AT12" s="1"/>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -11181,7 +11181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -11239,7 +11239,7 @@
       <c r="AS14" s="1"/>
       <c r="AT14" s="1"/>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -11295,7 +11295,7 @@
       <c r="AS15" s="1"/>
       <c r="AT15" s="1"/>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -11351,7 +11351,7 @@
       <c r="AS16" s="1"/>
       <c r="AT16" s="1"/>
     </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -11407,7 +11407,7 @@
       <c r="AS17" s="1"/>
       <c r="AT17" s="1"/>
     </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -11467,7 +11467,7 @@
       <c r="AS18" s="1"/>
       <c r="AT18" s="1"/>
     </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -11527,7 +11527,7 @@
       <c r="AS19" s="1"/>
       <c r="AT19" s="1"/>
     </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -11581,7 +11581,7 @@
       <c r="AS20" s="1"/>
       <c r="AT20" s="1"/>
     </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -11635,7 +11635,7 @@
       <c r="AS21" s="1"/>
       <c r="AT21" s="1"/>
     </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -11703,7 +11703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -11761,7 +11761,7 @@
       <c r="AS23" s="1"/>
       <c r="AT23" s="1"/>
     </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -11825,7 +11825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -11881,7 +11881,7 @@
       <c r="AS25" s="1"/>
       <c r="AT25" s="1"/>
     </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -11947,7 +11947,7 @@
       <c r="AS26" s="1"/>
       <c r="AT26" s="1"/>
     </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -12007,7 +12007,7 @@
       <c r="AS27" s="1"/>
       <c r="AT27" s="1"/>
     </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -12063,7 +12063,7 @@
       <c r="AS28" s="1"/>
       <c r="AT28" s="1"/>
     </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -12119,7 +12119,7 @@
       <c r="AS29" s="1"/>
       <c r="AT29" s="1"/>
     </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -12177,7 +12177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -12233,7 +12233,7 @@
       <c r="AS31" s="1"/>
       <c r="AT31" s="1"/>
     </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -12291,7 +12291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -12347,7 +12347,7 @@
       <c r="AS33" s="1"/>
       <c r="AT33" s="1"/>
     </row>
-    <row r="34" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -12409,7 +12409,7 @@
       <c r="AS34" s="1"/>
       <c r="AT34" s="1"/>
     </row>
-    <row r="35" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -12467,7 +12467,7 @@
       <c r="AS35" s="1"/>
       <c r="AT35" s="1"/>
     </row>
-    <row r="36" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -12521,7 +12521,7 @@
       <c r="AS36" s="1"/>
       <c r="AT36" s="1"/>
     </row>
-    <row r="37" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -12579,7 +12579,7 @@
       <c r="AS37" s="1"/>
       <c r="AT37" s="1"/>
     </row>
-    <row r="38" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -12635,7 +12635,7 @@
       <c r="AS38" s="1"/>
       <c r="AT38" s="1"/>
     </row>
-    <row r="39" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -12695,7 +12695,7 @@
       <c r="AS39" s="1"/>
       <c r="AT39" s="1"/>
     </row>
-    <row r="40" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -12751,7 +12751,7 @@
       <c r="AS40" s="1"/>
       <c r="AT40" s="1"/>
     </row>
-    <row r="41" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -12805,7 +12805,7 @@
       <c r="AS41" s="1"/>
       <c r="AT41" s="1"/>
     </row>
-    <row r="42" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -12861,7 +12861,7 @@
       <c r="AS42" s="1"/>
       <c r="AT42" s="1"/>
     </row>
-    <row r="43" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -12921,7 +12921,7 @@
       <c r="AS43" s="1"/>
       <c r="AT43" s="1"/>
     </row>
-    <row r="44" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -12977,7 +12977,7 @@
       <c r="AS44" s="1"/>
       <c r="AT44" s="1"/>
     </row>
-    <row r="45" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -13033,7 +13033,7 @@
       <c r="AS45" s="1"/>
       <c r="AT45" s="1"/>
     </row>
-    <row r="46" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -13091,7 +13091,7 @@
       <c r="AS46" s="1"/>
       <c r="AT46" s="1"/>
     </row>
-    <row r="47" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -13149,7 +13149,7 @@
       <c r="AS47" s="1"/>
       <c r="AT47" s="1"/>
     </row>
-    <row r="48" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -13209,7 +13209,7 @@
       <c r="AS48" s="1"/>
       <c r="AT48" s="1"/>
     </row>
-    <row r="49" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -13267,7 +13267,7 @@
       <c r="AS49" s="1"/>
       <c r="AT49" s="1"/>
     </row>
-    <row r="50" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -13329,7 +13329,7 @@
       <c r="AS50" s="1"/>
       <c r="AT50" s="1"/>
     </row>
-    <row r="51" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -13387,7 +13387,7 @@
       <c r="AS51" s="1"/>
       <c r="AT51" s="1"/>
     </row>
-    <row r="52" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -13441,7 +13441,7 @@
       <c r="AS52" s="1"/>
       <c r="AT52" s="1"/>
     </row>
-    <row r="53" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -13501,7 +13501,7 @@
       <c r="AS53" s="1"/>
       <c r="AT53" s="1"/>
     </row>
-    <row r="54" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:46" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -16399,6 +16399,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19638,7 +19639,7 @@
     <col min="46" max="48" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19772,7 +19773,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -19828,7 +19829,7 @@
       <c r="AU2" s="5"/>
       <c r="AV2" s="1"/>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -19886,7 +19887,7 @@
       <c r="AU3" s="5"/>
       <c r="AV3" s="1"/>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -19942,7 +19943,7 @@
       <c r="AU4" s="5"/>
       <c r="AV4" s="1"/>
     </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -19996,7 +19997,7 @@
       <c r="AU5" s="5"/>
       <c r="AV5" s="1"/>
     </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -20058,7 +20059,7 @@
       <c r="AU6" s="5"/>
       <c r="AV6" s="1"/>
     </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -20114,7 +20115,7 @@
       <c r="AU7" s="5"/>
       <c r="AV7" s="1"/>
     </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -20168,7 +20169,7 @@
       <c r="AU8" s="5"/>
       <c r="AV8" s="1"/>
     </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -20222,7 +20223,7 @@
       <c r="AU9" s="5"/>
       <c r="AV9" s="1"/>
     </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -20280,7 +20281,7 @@
       <c r="AU10" s="5"/>
       <c r="AV10" s="1"/>
     </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -20338,7 +20339,7 @@
       <c r="AU11" s="1"/>
       <c r="AV11" s="1"/>
     </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -20392,7 +20393,7 @@
       <c r="AU12" s="5"/>
       <c r="AV12" s="1"/>
     </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -20446,7 +20447,7 @@
       <c r="AU13" s="5"/>
       <c r="AV13" s="1"/>
     </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -20502,7 +20503,7 @@
       <c r="AU14" s="5"/>
       <c r="AV14" s="1"/>
     </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -20556,7 +20557,7 @@
       <c r="AU15" s="5"/>
       <c r="AV15" s="1"/>
     </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -20612,7 +20613,7 @@
       <c r="AU16" s="5"/>
       <c r="AV16" s="1"/>
     </row>
-    <row r="17" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -20668,7 +20669,7 @@
       <c r="AU17" s="5"/>
       <c r="AV17" s="1"/>
     </row>
-    <row r="18" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -20730,7 +20731,7 @@
       <c r="AU18" s="5"/>
       <c r="AV18" s="1"/>
     </row>
-    <row r="19" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -20792,7 +20793,7 @@
       <c r="AU19" s="5"/>
       <c r="AV19" s="1"/>
     </row>
-    <row r="20" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -20850,7 +20851,7 @@
       <c r="AU20" s="5"/>
       <c r="AV20" s="1"/>
     </row>
-    <row r="21" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>20</v>
       </c>
@@ -20912,7 +20913,7 @@
       <c r="AU21" s="5"/>
       <c r="AV21" s="1"/>
     </row>
-    <row r="22" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -20966,7 +20967,7 @@
       <c r="AU22" s="5"/>
       <c r="AV22" s="1"/>
     </row>
-    <row r="23" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -21020,7 +21021,7 @@
       <c r="AU23" s="5"/>
       <c r="AV23" s="1"/>
     </row>
-    <row r="24" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -21080,7 +21081,7 @@
       <c r="AU24" s="5"/>
       <c r="AV24" s="1"/>
     </row>
-    <row r="25" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -21140,7 +21141,7 @@
       <c r="AU25" s="5"/>
       <c r="AV25" s="1"/>
     </row>
-    <row r="26" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -21202,7 +21203,7 @@
       <c r="AU26" s="5"/>
       <c r="AV26" s="1"/>
     </row>
-    <row r="27" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -21256,7 +21257,7 @@
       <c r="AU27" s="5"/>
       <c r="AV27" s="1"/>
     </row>
-    <row r="28" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -21314,7 +21315,7 @@
       <c r="AU28" s="5"/>
       <c r="AV28" s="1"/>
     </row>
-    <row r="29" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -21370,7 +21371,7 @@
       <c r="AU29" s="5"/>
       <c r="AV29" s="1"/>
     </row>
-    <row r="30" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -21426,7 +21427,7 @@
       <c r="AU30" s="5"/>
       <c r="AV30" s="1"/>
     </row>
-    <row r="31" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>30</v>
       </c>
@@ -21486,7 +21487,7 @@
       <c r="AU31" s="5"/>
       <c r="AV31" s="1"/>
     </row>
-    <row r="32" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -21542,7 +21543,7 @@
       <c r="AU32" s="5"/>
       <c r="AV32" s="1"/>
     </row>
-    <row r="33" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -21596,7 +21597,7 @@
       <c r="AU33" s="1"/>
       <c r="AV33" s="1"/>
     </row>
-    <row r="34" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -21656,7 +21657,7 @@
       <c r="AU34" s="5"/>
       <c r="AV34" s="1"/>
     </row>
-    <row r="35" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -21710,7 +21711,7 @@
       <c r="AU35" s="1"/>
       <c r="AV35" s="1"/>
     </row>
-    <row r="36" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>35</v>
       </c>
@@ -21770,7 +21771,7 @@
       <c r="AU36" s="5"/>
       <c r="AV36" s="1"/>
     </row>
-    <row r="37" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -21824,7 +21825,7 @@
       <c r="AU37" s="5"/>
       <c r="AV37" s="1"/>
     </row>
-    <row r="38" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -21880,7 +21881,7 @@
       <c r="AU38" s="5"/>
       <c r="AV38" s="1"/>
     </row>
-    <row r="39" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>38</v>
       </c>
@@ -21940,7 +21941,7 @@
       <c r="AU39" s="5"/>
       <c r="AV39" s="1"/>
     </row>
-    <row r="40" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -21996,7 +21997,7 @@
       <c r="AU40" s="5"/>
       <c r="AV40" s="1"/>
     </row>
-    <row r="41" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -22054,7 +22055,7 @@
       <c r="AU41" s="5"/>
       <c r="AV41" s="1"/>
     </row>
-    <row r="42" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -22116,7 +22117,7 @@
       <c r="AU42" s="1"/>
       <c r="AV42" s="1"/>
     </row>
-    <row r="43" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -22174,7 +22175,7 @@
       <c r="AU43" s="1"/>
       <c r="AV43" s="1"/>
     </row>
-    <row r="44" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -22230,7 +22231,7 @@
       <c r="AU44" s="1"/>
       <c r="AV44" s="1"/>
     </row>
-    <row r="45" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45">
         <f t="shared" ref="A45:A201" si="0">A44+1</f>
         <v>44</v>
@@ -22276,7 +22277,7 @@
       <c r="AU45" s="1"/>
       <c r="AV45" s="1"/>
     </row>
-    <row r="46" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -22330,7 +22331,7 @@
       <c r="AU46" s="1"/>
       <c r="AV46" s="1"/>
     </row>
-    <row r="47" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -22376,7 +22377,7 @@
       <c r="AU47" s="1"/>
       <c r="AV47" s="1"/>
     </row>
-    <row r="48" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -22428,7 +22429,7 @@
       <c r="AU48" s="1"/>
       <c r="AV48" s="1"/>
     </row>
-    <row r="49" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -22474,7 +22475,7 @@
       <c r="AU49" s="1"/>
       <c r="AV49" s="1"/>
     </row>
-    <row r="50" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -22525,7 +22526,7 @@
       <c r="AU50" s="1"/>
       <c r="AV50" s="1"/>
     </row>
-    <row r="51" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -22571,7 +22572,7 @@
       <c r="AU51" s="1"/>
       <c r="AV51" s="1"/>
     </row>
-    <row r="52" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -22621,7 +22622,7 @@
       <c r="AU52" s="1"/>
       <c r="AV52" s="1"/>
     </row>
-    <row r="53" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -22669,7 +22670,7 @@
       <c r="AU53" s="1"/>
       <c r="AV53" s="1"/>
     </row>
-    <row r="54" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:48" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>53</v>
